--- a/SGC-CKN/Excel/1c1f041a-e12c-413f-a5dc-b9f2f4fc1735_Lô_đất_ký_hiệu_CT-02_P11-79_D800_21-03-2026.xlsx
+++ b/SGC-CKN/Excel/1c1f041a-e12c-413f-a5dc-b9f2f4fc1735_Lô_đất_ký_hiệu_CT-02_P11-79_D800_21-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="65">
   <si>
     <t>Dự án</t>
   </si>
@@ -53,7 +53,7 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>06:20 21/03/2026</t>
+    <t>01:20 21/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
@@ -184,10 +184,6 @@
   </si>
   <si>
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:39
-21/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">14:42
@@ -1399,10 +1395,10 @@
         <v>53</v>
       </c>
       <c r="D18" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>54</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>55</v>
       </c>
       <c r="F18" s="28">
         <v>-44.8</v>
@@ -1411,13 +1407,13 @@
         <v>-49.69</v>
       </c>
       <c r="H18" s="28">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="I18" s="28">
         <v>4.89</v>
       </c>
       <c r="J18" s="15">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1425,7 +1421,7 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1531,31 +1527,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1781,18 +1777,18 @@
         <v>-49.69</v>
       </c>
       <c r="G9" s="28">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H9" s="28">
         <v>4.89</v>
       </c>
       <c r="I9" s="15">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>30</v>
@@ -1810,13 +1806,13 @@
         <v>-49.69</v>
       </c>
       <c r="G10" s="33">
-        <v>8.68</v>
+        <v>8.7</v>
       </c>
       <c r="H10" s="33">
         <v>49.06</v>
       </c>
       <c r="I10" s="33">
-        <v>5.65</v>
+        <v>5.64</v>
       </c>
     </row>
   </sheetData>
